--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126421311</v>
+        <v>126419250</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,39 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587162</v>
+        <v>587280</v>
       </c>
       <c r="R3" t="n">
-        <v>6986535</v>
+        <v>6986216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126419250</v>
+        <v>126421311</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,34 +889,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587280</v>
+        <v>587162</v>
       </c>
       <c r="R4" t="n">
-        <v>6986216</v>
+        <v>6986535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,6 +954,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1087,32 +1087,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126418710</v>
+        <v>126415521</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>97230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587267</v>
+        <v>587428</v>
       </c>
       <c r="R6" t="n">
-        <v>6986111</v>
+        <v>6986050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,32 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126415521</v>
+        <v>126418710</v>
       </c>
       <c r="B7" t="n">
-        <v>97230</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587428</v>
+        <v>587267</v>
       </c>
       <c r="R7" t="n">
-        <v>6986050</v>
+        <v>6986111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,50 +1388,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126417465</v>
+        <v>126418654</v>
       </c>
       <c r="B9" t="n">
-        <v>57653</v>
+        <v>91207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587345</v>
+        <v>587315</v>
       </c>
       <c r="R9" t="n">
-        <v>6985976</v>
+        <v>6986068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,45 +1485,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126418654</v>
+        <v>126417465</v>
       </c>
       <c r="B10" t="n">
-        <v>91207</v>
+        <v>57653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587315</v>
+        <v>587345</v>
       </c>
       <c r="R10" t="n">
-        <v>6986068</v>
+        <v>6985976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126416247</v>
+        <v>126419173</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,39 +1705,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587340</v>
+        <v>587228</v>
       </c>
       <c r="R12" t="n">
-        <v>6986065</v>
+        <v>6986166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,11 +1765,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1801,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126419276</v>
+        <v>126421307</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,39 +1802,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587199</v>
+        <v>587162</v>
       </c>
       <c r="R13" t="n">
-        <v>6986088</v>
+        <v>6986535</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126419173</v>
+        <v>126419276</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,34 +1996,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587228</v>
+        <v>587199</v>
       </c>
       <c r="R15" t="n">
-        <v>6986166</v>
+        <v>6986088</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,6 +2061,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126421307</v>
+        <v>126416247</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,34 +2103,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587162</v>
+        <v>587340</v>
       </c>
       <c r="R16" t="n">
-        <v>6986535</v>
+        <v>6986065</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,6 +2168,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126421667</v>
+        <v>126420358</v>
       </c>
       <c r="B17" t="n">
-        <v>80080</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,34 +2210,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587333</v>
+        <v>586927</v>
       </c>
       <c r="R17" t="n">
-        <v>6986162</v>
+        <v>6986284</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,6 +2275,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2296,45 +2306,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126417734</v>
+        <v>126417127</v>
       </c>
       <c r="B18" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587384</v>
+        <v>587342</v>
       </c>
       <c r="R18" t="n">
-        <v>6986025</v>
+        <v>6985908</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2371,7 +2386,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2398,10 +2413,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126417127</v>
+        <v>126421667</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2409,39 +2424,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587342</v>
+        <v>587333</v>
       </c>
       <c r="R19" t="n">
-        <v>6985908</v>
+        <v>6986162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,11 +2484,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2505,50 +2510,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126420358</v>
+        <v>126417734</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586927</v>
+        <v>587384</v>
       </c>
       <c r="R20" t="n">
-        <v>6986284</v>
+        <v>6986025</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2709,37 +2709,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126416898</v>
+        <v>126419908</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2748,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587390</v>
+        <v>587178</v>
       </c>
       <c r="R22" t="n">
-        <v>6985939</v>
+        <v>6986327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2784,6 +2785,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Äldre hack som återanvänds där av färsk sav/kåda från hålen runnit ut.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,38 +2816,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126419908</v>
+        <v>126416898</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2850,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587178</v>
+        <v>587390</v>
       </c>
       <c r="R23" t="n">
-        <v>6986327</v>
+        <v>6985939</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,11 +2891,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Äldre hack som återanvänds där av färsk sav/kåda från hålen runnit ut.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,32 +3018,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126416572</v>
+        <v>126417452</v>
       </c>
       <c r="B25" t="n">
-        <v>91696</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587430</v>
+        <v>587363</v>
       </c>
       <c r="R25" t="n">
-        <v>6985944</v>
+        <v>6985986</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3089,6 +3089,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Upprepande inom området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126417452</v>
+        <v>126420423</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3126,34 +3131,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587363</v>
+        <v>586945</v>
       </c>
       <c r="R26" t="n">
-        <v>6985986</v>
+        <v>6986278</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,7 +3200,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Upprepande inom området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3217,10 +3227,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126420423</v>
+        <v>126415315</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3228,39 +3238,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586945</v>
+        <v>587472</v>
       </c>
       <c r="R27" t="n">
-        <v>6986278</v>
+        <v>6986072</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3293,11 +3298,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3421,7 +3421,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126415315</v>
+        <v>126416847</v>
       </c>
       <c r="B29" t="n">
         <v>78977</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587472</v>
+        <v>587406</v>
       </c>
       <c r="R29" t="n">
-        <v>6986072</v>
+        <v>6985908</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126416847</v>
+        <v>126419617</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>91538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587406</v>
+        <v>587192</v>
       </c>
       <c r="R30" t="n">
-        <v>6985908</v>
+        <v>6986314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126417368</v>
+        <v>126421256</v>
       </c>
       <c r="B31" t="n">
         <v>57656</v>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587328</v>
+        <v>587185</v>
       </c>
       <c r="R31" t="n">
-        <v>6985952</v>
+        <v>6986510</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3722,10 +3722,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126418994</v>
+        <v>126419964</v>
       </c>
       <c r="B32" t="n">
-        <v>57816</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3733,31 +3733,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3766,10 +3762,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587241</v>
+        <v>586981</v>
       </c>
       <c r="R32" t="n">
-        <v>6986122</v>
+        <v>6986245</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,7 +3802,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3 rör sig mellan träden pratar med varandra</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3833,7 +3829,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126419964</v>
+        <v>126417368</v>
       </c>
       <c r="B33" t="n">
         <v>57656</v>
@@ -3873,10 +3869,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586981</v>
+        <v>587328</v>
       </c>
       <c r="R33" t="n">
-        <v>6986245</v>
+        <v>6985952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126419617</v>
+        <v>126418994</v>
       </c>
       <c r="B34" t="n">
-        <v>91538</v>
+        <v>57816</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,34 +3947,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587192</v>
+        <v>587241</v>
       </c>
       <c r="R34" t="n">
-        <v>6986314</v>
+        <v>6986122</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4011,6 +4016,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 rör sig mellan träden pratar med varandra</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4037,10 +4047,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126421256</v>
+        <v>126419223</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,39 +4058,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587185</v>
+        <v>587226</v>
       </c>
       <c r="R35" t="n">
-        <v>6986510</v>
+        <v>6986030</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4113,11 +4118,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4144,45 +4144,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126419468</v>
+        <v>126421388</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
+        <v>57656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587187</v>
+        <v>587216</v>
       </c>
       <c r="R36" t="n">
-        <v>6986221</v>
+        <v>6986485</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4215,6 +4220,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4241,50 +4251,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126421388</v>
+        <v>126419468</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>98269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587216</v>
+        <v>587187</v>
       </c>
       <c r="R37" t="n">
-        <v>6986485</v>
+        <v>6986221</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,11 +4322,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4348,10 +4348,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126419223</v>
+        <v>126418669</v>
       </c>
       <c r="B38" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4359,21 +4359,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587226</v>
+        <v>587315</v>
       </c>
       <c r="R38" t="n">
-        <v>6986030</v>
+        <v>6986068</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126418669</v>
+        <v>126418977</v>
       </c>
       <c r="B40" t="n">
         <v>91242</v>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587315</v>
+        <v>587250</v>
       </c>
       <c r="R40" t="n">
-        <v>6986068</v>
+        <v>6986130</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4639,49 +4639,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126416029</v>
+        <v>126421008</v>
       </c>
       <c r="B41" t="n">
-        <v>98269</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587398</v>
+        <v>587170</v>
       </c>
       <c r="R41" t="n">
-        <v>6986000</v>
+        <v>6986399</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4740,49 +4736,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126417679</v>
+        <v>126419681</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>91696</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587381</v>
+        <v>587210</v>
       </c>
       <c r="R42" t="n">
-        <v>6986014</v>
+        <v>6986334</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4815,11 +4807,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4846,45 +4833,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126418977</v>
+        <v>126417679</v>
       </c>
       <c r="B43" t="n">
-        <v>91242</v>
+        <v>98269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587250</v>
+        <v>587381</v>
       </c>
       <c r="R43" t="n">
-        <v>6986130</v>
+        <v>6986014</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,6 +4908,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4943,45 +4939,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126419681</v>
+        <v>126416029</v>
       </c>
       <c r="B44" t="n">
-        <v>91696</v>
+        <v>98269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587210</v>
+        <v>587398</v>
       </c>
       <c r="R44" t="n">
-        <v>6986334</v>
+        <v>6986000</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126421008</v>
+        <v>126421544</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>56839</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,34 +5051,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587170</v>
+        <v>587257</v>
       </c>
       <c r="R45" t="n">
-        <v>6986399</v>
+        <v>6986219</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5111,6 +5119,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Järpeunge som sitter på trädgrenen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5234,10 +5247,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126421544</v>
+        <v>126417263</v>
       </c>
       <c r="B47" t="n">
-        <v>56839</v>
+        <v>57656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,16 +5258,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5262,25 +5275,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587257</v>
+        <v>587361</v>
       </c>
       <c r="R47" t="n">
-        <v>6986219</v>
+        <v>6985937</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5317,7 +5327,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Järpeunge som sitter på trädgrenen.</t>
+          <t>Ringhack av tretåig hackspett på gran, rinner ur dom äldre återanvända hack hålen</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5558,10 +5568,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126417263</v>
+        <v>126416938</v>
       </c>
       <c r="B50" t="n">
-        <v>57656</v>
+        <v>88651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5569,29 +5579,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
@@ -5634,11 +5639,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran, rinner ur dom äldre återanvända hack hålen</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5762,10 +5762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126419739</v>
+        <v>126419122</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,39 +5773,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587036</v>
+        <v>587216</v>
       </c>
       <c r="R52" t="n">
-        <v>6986280</v>
+        <v>6986114</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5838,11 +5833,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5869,7 +5859,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126420043</v>
+        <v>126419739</v>
       </c>
       <c r="B53" t="n">
         <v>57656</v>
@@ -5909,13 +5899,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587176</v>
+        <v>587036</v>
       </c>
       <c r="R53" t="n">
-        <v>6986320</v>
+        <v>6986280</v>
       </c>
       <c r="S53" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5949,7 +5939,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall många</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5976,10 +5966,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126416938</v>
+        <v>126420043</v>
       </c>
       <c r="B54" t="n">
-        <v>88651</v>
+        <v>57656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5987,37 +5977,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>587361</v>
+        <v>587176</v>
       </c>
       <c r="R54" t="n">
-        <v>6985937</v>
+        <v>6986320</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6047,6 +6042,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall många</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126419122</v>
+        <v>126417916</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6186,21 +6186,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587216</v>
+        <v>587395</v>
       </c>
       <c r="R56" t="n">
-        <v>6986114</v>
+        <v>6986032</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6272,10 +6272,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126419561</v>
+        <v>126421649</v>
       </c>
       <c r="B57" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6283,39 +6283,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587198</v>
+        <v>587297</v>
       </c>
       <c r="R57" t="n">
-        <v>6986233</v>
+        <v>6986177</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6348,11 +6343,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6486,10 +6476,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126417916</v>
+        <v>126419561</v>
       </c>
       <c r="B59" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6497,34 +6487,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587395</v>
+        <v>587198</v>
       </c>
       <c r="R59" t="n">
-        <v>6986032</v>
+        <v>6986233</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6557,6 +6552,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6583,32 +6583,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126421649</v>
+        <v>126416782</v>
       </c>
       <c r="B60" t="n">
-        <v>80081</v>
+        <v>98373</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>587297</v>
+        <v>587390</v>
       </c>
       <c r="R60" t="n">
-        <v>6986177</v>
+        <v>6985939</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6879,7 +6879,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126416782</v>
+        <v>126416113</v>
       </c>
       <c r="B63" t="n">
         <v>98373</v>
@@ -6907,17 +6907,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>587390</v>
+        <v>587402</v>
       </c>
       <c r="R63" t="n">
-        <v>6985939</v>
+        <v>6985981</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6950,6 +6954,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området 10+</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6976,49 +6985,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126416113</v>
+        <v>126418597</v>
       </c>
       <c r="B64" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587402</v>
+        <v>587303</v>
       </c>
       <c r="R64" t="n">
-        <v>6985981</v>
+        <v>6986119</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7051,11 +7056,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området 10+</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7189,32 +7189,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126418597</v>
+        <v>126418130</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7224,10 +7224,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>587303</v>
+        <v>587352</v>
       </c>
       <c r="R66" t="n">
-        <v>6986119</v>
+        <v>6986053</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7260,6 +7260,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av dom inom området</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7286,10 +7291,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126420995</v>
+        <v>126421604</v>
       </c>
       <c r="B67" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7297,39 +7302,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>587147</v>
+        <v>587297</v>
       </c>
       <c r="R67" t="n">
-        <v>6986409</v>
+        <v>6986177</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7362,11 +7362,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7393,10 +7388,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126421604</v>
+        <v>126420995</v>
       </c>
       <c r="B68" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7404,34 +7399,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>587297</v>
+        <v>587147</v>
       </c>
       <c r="R68" t="n">
-        <v>6986177</v>
+        <v>6986409</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7464,6 +7464,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7490,45 +7495,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126418130</v>
+        <v>126426434</v>
       </c>
       <c r="B69" t="n">
-        <v>98373</v>
+        <v>57816</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>587352</v>
+        <v>587463</v>
       </c>
       <c r="R69" t="n">
-        <v>6986053</v>
+        <v>6986055</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7555,17 +7569,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Riklig förekomst av dom inom området</t>
+          <t>2 gör läten i träden</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7589,6 +7603,103 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126425417</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Utsikten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>587365</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6985886</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126416064</v>
+        <v>126419250</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587402</v>
+        <v>587280</v>
       </c>
       <c r="R2" t="n">
-        <v>6985981</v>
+        <v>6986216</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av dom inom området</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126419250</v>
+        <v>126421311</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587280</v>
+        <v>587162</v>
       </c>
       <c r="R3" t="n">
-        <v>6986216</v>
+        <v>6986535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,38 +879,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126421311</v>
+        <v>126416064</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587162</v>
+        <v>587402</v>
       </c>
       <c r="R4" t="n">
-        <v>6986535</v>
+        <v>6985981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Riklig förekomst av dom inom området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1087,32 +1087,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126415521</v>
+        <v>126418710</v>
       </c>
       <c r="B6" t="n">
-        <v>97230</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587428</v>
+        <v>587267</v>
       </c>
       <c r="R6" t="n">
-        <v>6986050</v>
+        <v>6986111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126418710</v>
+        <v>126416142</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,34 +1195,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587267</v>
+        <v>587352</v>
       </c>
       <c r="R7" t="n">
-        <v>6986111</v>
+        <v>6986053</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,6 +1260,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,50 +1291,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126416142</v>
+        <v>126415521</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587352</v>
+        <v>587428</v>
       </c>
       <c r="R8" t="n">
-        <v>6986053</v>
+        <v>6986050</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,11 +1362,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,45 +1388,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126418654</v>
+        <v>126419125</v>
       </c>
       <c r="B9" t="n">
-        <v>91207</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587315</v>
+        <v>587228</v>
       </c>
       <c r="R9" t="n">
-        <v>6986068</v>
+        <v>6986166</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1464,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall *</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,50 +1495,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126417465</v>
+        <v>126418654</v>
       </c>
       <c r="B10" t="n">
-        <v>57653</v>
+        <v>91207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587345</v>
+        <v>587315</v>
       </c>
       <c r="R10" t="n">
-        <v>6985976</v>
+        <v>6986068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126419125</v>
+        <v>126417465</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,16 +1603,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1618,7 +1623,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1627,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587228</v>
+        <v>587345</v>
       </c>
       <c r="R11" t="n">
-        <v>6986166</v>
+        <v>6985976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,11 +1668,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall *</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2917,49 +2917,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126415932</v>
+        <v>126417452</v>
       </c>
       <c r="B24" t="n">
-        <v>98256</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587398</v>
+        <v>587363</v>
       </c>
       <c r="R24" t="n">
-        <v>6986011</v>
+        <v>6985986</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2992,6 +2988,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Upprepande inom området</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3018,10 +3019,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126417452</v>
+        <v>126420423</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3029,34 +3030,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587363</v>
+        <v>586945</v>
       </c>
       <c r="R25" t="n">
-        <v>6985986</v>
+        <v>6986278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,7 +3099,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Upprepande inom området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3120,38 +3126,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126420423</v>
+        <v>126415932</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>98256</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3160,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586945</v>
+        <v>587398</v>
       </c>
       <c r="R26" t="n">
-        <v>6986278</v>
+        <v>6986011</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,11 +3201,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4047,32 +4047,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126419223</v>
+        <v>126419468</v>
       </c>
       <c r="B35" t="n">
-        <v>80080</v>
+        <v>98269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587226</v>
+        <v>587187</v>
       </c>
       <c r="R35" t="n">
-        <v>6986030</v>
+        <v>6986221</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4144,10 +4144,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126421388</v>
+        <v>126419223</v>
       </c>
       <c r="B36" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4155,39 +4155,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587216</v>
+        <v>587226</v>
       </c>
       <c r="R36" t="n">
-        <v>6986485</v>
+        <v>6986030</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,11 +4215,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4251,45 +4241,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126419468</v>
+        <v>126421388</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
+        <v>57656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587187</v>
+        <v>587216</v>
       </c>
       <c r="R37" t="n">
-        <v>6986221</v>
+        <v>6986485</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4322,6 +4317,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5040,10 +5040,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126421544</v>
+        <v>126421920</v>
       </c>
       <c r="B45" t="n">
-        <v>56839</v>
+        <v>91260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,42 +5051,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587257</v>
+        <v>587478</v>
       </c>
       <c r="R45" t="n">
-        <v>6986219</v>
+        <v>6986044</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5119,11 +5111,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Järpeunge som sitter på trädgrenen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5150,10 +5137,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126421920</v>
+        <v>126421544</v>
       </c>
       <c r="B46" t="n">
-        <v>91260</v>
+        <v>56839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5161,34 +5148,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587478</v>
+        <v>587257</v>
       </c>
       <c r="R46" t="n">
-        <v>6986044</v>
+        <v>6986219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5221,6 +5216,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Järpeunge som sitter på trädgrenen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126417916</v>
+        <v>126421649</v>
       </c>
       <c r="B56" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6186,21 +6186,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587395</v>
+        <v>587297</v>
       </c>
       <c r="R56" t="n">
-        <v>6986032</v>
+        <v>6986177</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6272,10 +6272,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126421649</v>
+        <v>126417916</v>
       </c>
       <c r="B57" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6283,21 +6283,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587297</v>
+        <v>587395</v>
       </c>
       <c r="R57" t="n">
-        <v>6986177</v>
+        <v>6986032</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126419250</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126421311</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126416064</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>126418274</v>
       </c>
       <c r="B5" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126418710</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126416142</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>126415521</v>
       </c>
       <c r="B8" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126419125</v>
+        <v>126417465</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,16 +1399,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1419,7 +1419,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587228</v>
+        <v>587345</v>
       </c>
       <c r="R9" t="n">
-        <v>6986166</v>
+        <v>6985976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,11 +1464,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall *</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,45 +1490,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126418654</v>
+        <v>126419125</v>
       </c>
       <c r="B10" t="n">
-        <v>91207</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587315</v>
+        <v>587228</v>
       </c>
       <c r="R10" t="n">
-        <v>6986068</v>
+        <v>6986166</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,6 +1566,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall *</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,50 +1597,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126417465</v>
+        <v>126418654</v>
       </c>
       <c r="B11" t="n">
-        <v>57653</v>
+        <v>91210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587345</v>
+        <v>587315</v>
       </c>
       <c r="R11" t="n">
-        <v>6985976</v>
+        <v>6986068</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,7 +1697,7 @@
         <v>126419173</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126421307</v>
+        <v>126419158</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>80111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587162</v>
+        <v>587227</v>
       </c>
       <c r="R13" t="n">
-        <v>6986535</v>
+        <v>6986101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126419158</v>
+        <v>126421307</v>
       </c>
       <c r="B14" t="n">
-        <v>80108</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587227</v>
+        <v>587162</v>
       </c>
       <c r="R14" t="n">
-        <v>6986101</v>
+        <v>6986535</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1988,7 +1988,7 @@
         <v>126419276</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>126416247</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126420358</v>
+        <v>126421667</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>80083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,39 +2210,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586927</v>
+        <v>587333</v>
       </c>
       <c r="R17" t="n">
-        <v>6986284</v>
+        <v>6986162</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2275,11 +2270,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2306,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126417127</v>
+        <v>126420358</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587342</v>
+        <v>586927</v>
       </c>
       <c r="R18" t="n">
-        <v>6985908</v>
+        <v>6986284</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,10 +2403,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126421667</v>
+        <v>126417127</v>
       </c>
       <c r="B19" t="n">
-        <v>80080</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,34 +2414,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587333</v>
+        <v>587342</v>
       </c>
       <c r="R19" t="n">
-        <v>6986162</v>
+        <v>6985908</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,6 +2479,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2513,7 +2513,7 @@
         <v>126417734</v>
       </c>
       <c r="B20" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>126416041</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>126419908</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>126416898</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>126417452</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>126420423</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>126415932</v>
       </c>
       <c r="B26" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>126415315</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>126421612</v>
       </c>
       <c r="B28" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126416847</v>
+        <v>126419617</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>91541</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587406</v>
+        <v>587192</v>
       </c>
       <c r="R29" t="n">
-        <v>6985908</v>
+        <v>6986314</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126419617</v>
+        <v>126416847</v>
       </c>
       <c r="B30" t="n">
-        <v>91538</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587192</v>
+        <v>587406</v>
       </c>
       <c r="R30" t="n">
-        <v>6986314</v>
+        <v>6985908</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>126421256</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>126419964</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>126417368</v>
       </c>
       <c r="B33" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>126418994</v>
       </c>
       <c r="B34" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4047,32 +4047,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126419468</v>
+        <v>126419223</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
+        <v>80083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587187</v>
+        <v>587226</v>
       </c>
       <c r="R35" t="n">
-        <v>6986221</v>
+        <v>6986030</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4144,10 +4144,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126419223</v>
+        <v>126421388</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4155,34 +4155,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587226</v>
+        <v>587216</v>
       </c>
       <c r="R36" t="n">
-        <v>6986030</v>
+        <v>6986485</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4215,6 +4220,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4241,50 +4251,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126421388</v>
+        <v>126419468</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>98278</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587216</v>
+        <v>587187</v>
       </c>
       <c r="R37" t="n">
-        <v>6986485</v>
+        <v>6986221</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,11 +4322,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4351,7 +4351,7 @@
         <v>126418669</v>
       </c>
       <c r="B38" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>126416472</v>
       </c>
       <c r="B39" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4542,32 +4542,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126418977</v>
+        <v>126419681</v>
       </c>
       <c r="B40" t="n">
-        <v>91242</v>
+        <v>91699</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587250</v>
+        <v>587210</v>
       </c>
       <c r="R40" t="n">
-        <v>6986130</v>
+        <v>6986334</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4639,10 +4639,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126421008</v>
+        <v>126418977</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>91245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587170</v>
+        <v>587250</v>
       </c>
       <c r="R41" t="n">
-        <v>6986399</v>
+        <v>6986130</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4736,45 +4736,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126419681</v>
+        <v>126417679</v>
       </c>
       <c r="B42" t="n">
-        <v>91696</v>
+        <v>98278</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587210</v>
+        <v>587381</v>
       </c>
       <c r="R42" t="n">
-        <v>6986334</v>
+        <v>6986014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4807,6 +4811,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4833,10 +4842,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126417679</v>
+        <v>126416029</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4863,7 +4872,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4872,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587381</v>
+        <v>587398</v>
       </c>
       <c r="R43" t="n">
-        <v>6986014</v>
+        <v>6986000</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4908,11 +4917,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4939,49 +4943,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126416029</v>
+        <v>126421008</v>
       </c>
       <c r="B44" t="n">
-        <v>98269</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587398</v>
+        <v>587170</v>
       </c>
       <c r="R44" t="n">
-        <v>6986000</v>
+        <v>6986399</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5043,7 +5043,7 @@
         <v>126421920</v>
       </c>
       <c r="B45" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>126421544</v>
       </c>
       <c r="B46" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126417263</v>
       </c>
       <c r="B47" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>126419436</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>126421034</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126416938</v>
+        <v>126417472</v>
       </c>
       <c r="B50" t="n">
-        <v>88651</v>
+        <v>56233</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5579,34 +5579,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>206004</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587361</v>
+        <v>587363</v>
       </c>
       <c r="R50" t="n">
-        <v>6985937</v>
+        <v>6985986</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,10 +5670,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126418565</v>
+        <v>126416938</v>
       </c>
       <c r="B51" t="n">
-        <v>80080</v>
+        <v>88654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5676,21 +5681,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5700,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587314</v>
+        <v>587361</v>
       </c>
       <c r="R51" t="n">
-        <v>6986126</v>
+        <v>6985937</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5762,10 +5767,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126419122</v>
+        <v>126418565</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>80083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,21 +5778,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5797,10 +5802,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587216</v>
+        <v>587314</v>
       </c>
       <c r="R52" t="n">
-        <v>6986114</v>
+        <v>6986126</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5859,10 +5864,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126419739</v>
+        <v>126419122</v>
       </c>
       <c r="B53" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5870,39 +5875,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587036</v>
+        <v>587216</v>
       </c>
       <c r="R53" t="n">
-        <v>6986280</v>
+        <v>6986114</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5935,11 +5935,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5966,10 +5961,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126420043</v>
+        <v>126419739</v>
       </c>
       <c r="B54" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6006,13 +6001,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>587176</v>
+        <v>587036</v>
       </c>
       <c r="R54" t="n">
-        <v>6986320</v>
+        <v>6986280</v>
       </c>
       <c r="S54" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6046,7 +6041,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall många</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6073,10 +6068,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126417472</v>
+        <v>126420043</v>
       </c>
       <c r="B55" t="n">
-        <v>56232</v>
+        <v>57657</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6084,27 +6079,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6113,13 +6108,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>587363</v>
+        <v>587176</v>
       </c>
       <c r="R55" t="n">
-        <v>6985986</v>
+        <v>6986320</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6149,6 +6144,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall många</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126421649</v>
+        <v>126419079</v>
       </c>
       <c r="B56" t="n">
-        <v>80081</v>
+        <v>57657</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6186,34 +6186,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587297</v>
+        <v>587230</v>
       </c>
       <c r="R56" t="n">
-        <v>6986177</v>
+        <v>6986145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6246,6 +6251,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6272,10 +6282,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126417916</v>
+        <v>126419561</v>
       </c>
       <c r="B57" t="n">
-        <v>91260</v>
+        <v>57657</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6283,34 +6293,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587395</v>
+        <v>587198</v>
       </c>
       <c r="R57" t="n">
-        <v>6986032</v>
+        <v>6986233</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6343,6 +6358,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6369,10 +6389,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126419079</v>
+        <v>126417916</v>
       </c>
       <c r="B58" t="n">
-        <v>57656</v>
+        <v>91263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6380,39 +6400,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>587230</v>
+        <v>587395</v>
       </c>
       <c r="R58" t="n">
-        <v>6986145</v>
+        <v>6986032</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6445,11 +6460,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6476,10 +6486,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126419561</v>
+        <v>126421649</v>
       </c>
       <c r="B59" t="n">
-        <v>57656</v>
+        <v>80084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6487,39 +6497,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587198</v>
+        <v>587297</v>
       </c>
       <c r="R59" t="n">
-        <v>6986233</v>
+        <v>6986177</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6552,11 +6557,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6586,7 +6586,7 @@
         <v>126416782</v>
       </c>
       <c r="B60" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>126415654</v>
       </c>
       <c r="B61" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>126417018</v>
       </c>
       <c r="B62" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6879,37 +6879,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126416113</v>
+        <v>126420605</v>
       </c>
       <c r="B63" t="n">
-        <v>98373</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6918,10 +6919,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>587402</v>
+        <v>587012</v>
       </c>
       <c r="R63" t="n">
-        <v>6985981</v>
+        <v>6986341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6958,7 +6959,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området 10+</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6988,7 +6989,7 @@
         <v>126418597</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7082,38 +7083,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126420605</v>
+        <v>126416113</v>
       </c>
       <c r="B65" t="n">
-        <v>57656</v>
+        <v>98382</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587012</v>
+        <v>587402</v>
       </c>
       <c r="R65" t="n">
-        <v>6986341</v>
+        <v>6985981</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Riklig förekomst inom området 10+</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7189,45 +7189,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126418130</v>
+        <v>126420995</v>
       </c>
       <c r="B66" t="n">
-        <v>98373</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>587352</v>
+        <v>587147</v>
       </c>
       <c r="R66" t="n">
-        <v>6986053</v>
+        <v>6986409</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7264,7 +7269,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Riklig förekomst av dom inom området</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7294,7 +7299,7 @@
         <v>126421604</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7388,50 +7393,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126420995</v>
+        <v>126418130</v>
       </c>
       <c r="B68" t="n">
-        <v>57656</v>
+        <v>98382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>587147</v>
+        <v>587352</v>
       </c>
       <c r="R68" t="n">
-        <v>6986409</v>
+        <v>6986053</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Riklig förekomst av dom inom området</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7498,7 +7498,7 @@
         <v>126426434</v>
       </c>
       <c r="B69" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>126425417</v>
       </c>
       <c r="B70" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126419158</v>
+        <v>126421307</v>
       </c>
       <c r="B13" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587227</v>
+        <v>587162</v>
       </c>
       <c r="R13" t="n">
-        <v>6986101</v>
+        <v>6986535</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126421307</v>
+        <v>126419158</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587162</v>
+        <v>587227</v>
       </c>
       <c r="R14" t="n">
-        <v>6986535</v>
+        <v>6986101</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2612,45 +2612,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126416041</v>
+        <v>126416898</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587357</v>
+        <v>587390</v>
       </c>
       <c r="R21" t="n">
-        <v>6986029</v>
+        <v>6985939</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,49 +2820,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126416898</v>
+        <v>126416041</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587390</v>
+        <v>587357</v>
       </c>
       <c r="R23" t="n">
-        <v>6985939</v>
+        <v>6986029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4047,10 +4047,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126419223</v>
+        <v>126421388</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4058,34 +4058,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587226</v>
+        <v>587216</v>
       </c>
       <c r="R35" t="n">
-        <v>6986030</v>
+        <v>6986485</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4118,6 +4123,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4144,50 +4154,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126421388</v>
+        <v>126419468</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>98278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587216</v>
+        <v>587187</v>
       </c>
       <c r="R36" t="n">
-        <v>6986485</v>
+        <v>6986221</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,11 +4225,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4251,32 +4251,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126419468</v>
+        <v>126419223</v>
       </c>
       <c r="B37" t="n">
-        <v>98278</v>
+        <v>80083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587187</v>
+        <v>587226</v>
       </c>
       <c r="R37" t="n">
-        <v>6986221</v>
+        <v>6986030</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4348,32 +4348,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126418669</v>
+        <v>126416472</v>
       </c>
       <c r="B38" t="n">
-        <v>91245</v>
+        <v>80111</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587315</v>
+        <v>587331</v>
       </c>
       <c r="R38" t="n">
-        <v>6986068</v>
+        <v>6986098</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4445,32 +4445,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126416472</v>
+        <v>126418669</v>
       </c>
       <c r="B39" t="n">
-        <v>80111</v>
+        <v>91245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587331</v>
+        <v>587315</v>
       </c>
       <c r="R39" t="n">
-        <v>6986098</v>
+        <v>6986068</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4542,45 +4542,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126419681</v>
+        <v>126417679</v>
       </c>
       <c r="B40" t="n">
-        <v>91699</v>
+        <v>98278</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587210</v>
+        <v>587381</v>
       </c>
       <c r="R40" t="n">
-        <v>6986334</v>
+        <v>6986014</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4613,6 +4617,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4639,45 +4648,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126418977</v>
+        <v>126416029</v>
       </c>
       <c r="B41" t="n">
-        <v>91245</v>
+        <v>98278</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587250</v>
+        <v>587398</v>
       </c>
       <c r="R41" t="n">
-        <v>6986130</v>
+        <v>6986000</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4736,49 +4749,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126417679</v>
+        <v>126418977</v>
       </c>
       <c r="B42" t="n">
-        <v>98278</v>
+        <v>91245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587381</v>
+        <v>587250</v>
       </c>
       <c r="R42" t="n">
-        <v>6986014</v>
+        <v>6986130</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4811,11 +4820,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4842,49 +4846,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126416029</v>
+        <v>126419681</v>
       </c>
       <c r="B43" t="n">
-        <v>98278</v>
+        <v>91699</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587398</v>
+        <v>587210</v>
       </c>
       <c r="R43" t="n">
-        <v>6986000</v>
+        <v>6986334</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6175,10 +6175,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126419079</v>
+        <v>126417916</v>
       </c>
       <c r="B56" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6186,39 +6186,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587230</v>
+        <v>587395</v>
       </c>
       <c r="R56" t="n">
-        <v>6986145</v>
+        <v>6986032</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6251,11 +6246,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6282,10 +6272,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126419561</v>
+        <v>126421649</v>
       </c>
       <c r="B57" t="n">
-        <v>57657</v>
+        <v>80084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6293,39 +6283,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587198</v>
+        <v>587297</v>
       </c>
       <c r="R57" t="n">
-        <v>6986233</v>
+        <v>6986177</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6358,11 +6343,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6389,10 +6369,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126417916</v>
+        <v>126419079</v>
       </c>
       <c r="B58" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6400,34 +6380,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>587395</v>
+        <v>587230</v>
       </c>
       <c r="R58" t="n">
-        <v>6986032</v>
+        <v>6986145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6460,6 +6445,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6486,10 +6476,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126421649</v>
+        <v>126419561</v>
       </c>
       <c r="B59" t="n">
-        <v>80084</v>
+        <v>57657</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6497,34 +6487,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587297</v>
+        <v>587198</v>
       </c>
       <c r="R59" t="n">
-        <v>6986177</v>
+        <v>6986233</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6557,6 +6552,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6879,10 +6879,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126420605</v>
+        <v>126418597</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6890,39 +6890,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>587012</v>
+        <v>587303</v>
       </c>
       <c r="R63" t="n">
-        <v>6986341</v>
+        <v>6986119</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6955,11 +6950,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6986,10 +6976,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126418597</v>
+        <v>126420605</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6997,34 +6987,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587303</v>
+        <v>587012</v>
       </c>
       <c r="R64" t="n">
-        <v>6986119</v>
+        <v>6986341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,6 +7052,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7296,32 +7296,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126421604</v>
+        <v>126418130</v>
       </c>
       <c r="B67" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>587297</v>
+        <v>587352</v>
       </c>
       <c r="R67" t="n">
-        <v>6986177</v>
+        <v>6986053</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7367,6 +7367,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av dom inom området</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7393,32 +7398,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126418130</v>
+        <v>126421604</v>
       </c>
       <c r="B68" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7428,10 +7433,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>587352</v>
+        <v>587297</v>
       </c>
       <c r="R68" t="n">
-        <v>6986053</v>
+        <v>6986177</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7464,11 +7469,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av dom inom området</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126418710</v>
+        <v>126416142</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1098,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587267</v>
+        <v>587352</v>
       </c>
       <c r="R6" t="n">
-        <v>6986111</v>
+        <v>6986053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,6 +1163,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126416142</v>
+        <v>126418710</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,39 +1205,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587352</v>
+        <v>587267</v>
       </c>
       <c r="R7" t="n">
-        <v>6986053</v>
+        <v>6986111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,11 +1265,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,50 +1388,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126417465</v>
+        <v>126418654</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>91210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587345</v>
+        <v>587315</v>
       </c>
       <c r="R9" t="n">
-        <v>6985976</v>
+        <v>6986068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126419125</v>
+        <v>126417465</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,16 +1496,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1521,7 +1516,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1530,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587228</v>
+        <v>587345</v>
       </c>
       <c r="R10" t="n">
-        <v>6986166</v>
+        <v>6985976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall *</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,45 +1587,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126418654</v>
+        <v>126419125</v>
       </c>
       <c r="B11" t="n">
-        <v>91210</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587315</v>
+        <v>587228</v>
       </c>
       <c r="R11" t="n">
-        <v>6986068</v>
+        <v>6986166</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,6 +1663,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall *</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126419173</v>
+        <v>126419276</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,34 +1705,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587228</v>
+        <v>587199</v>
       </c>
       <c r="R12" t="n">
-        <v>6986166</v>
+        <v>6986088</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,6 +1770,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126421307</v>
+        <v>126416247</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,34 +1812,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587162</v>
+        <v>587340</v>
       </c>
       <c r="R13" t="n">
-        <v>6986535</v>
+        <v>6986065</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1877,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,32 +1908,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126419158</v>
+        <v>126419173</v>
       </c>
       <c r="B14" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587227</v>
+        <v>587228</v>
       </c>
       <c r="R14" t="n">
-        <v>6986101</v>
+        <v>6986166</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126419276</v>
+        <v>126421307</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,39 +2016,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587199</v>
+        <v>587162</v>
       </c>
       <c r="R15" t="n">
-        <v>6986088</v>
+        <v>6986535</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,11 +2076,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2092,50 +2102,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126416247</v>
+        <v>126419158</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587340</v>
+        <v>587227</v>
       </c>
       <c r="R16" t="n">
-        <v>6986065</v>
+        <v>6986101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,11 +2173,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2612,49 +2612,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126416898</v>
+        <v>126416041</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587390</v>
+        <v>587357</v>
       </c>
       <c r="R21" t="n">
-        <v>6985939</v>
+        <v>6986029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,45 +2816,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126416041</v>
+        <v>126416898</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587357</v>
+        <v>587390</v>
       </c>
       <c r="R23" t="n">
-        <v>6986029</v>
+        <v>6985939</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126417452</v>
+        <v>126420423</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,34 +2928,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587363</v>
+        <v>586945</v>
       </c>
       <c r="R24" t="n">
-        <v>6985986</v>
+        <v>6986278</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2992,7 +2997,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Upprepande inom området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3019,38 +3024,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126420423</v>
+        <v>126415932</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3059,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586945</v>
+        <v>587398</v>
       </c>
       <c r="R25" t="n">
-        <v>6986278</v>
+        <v>6986011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,11 +3099,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3126,49 +3125,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126415932</v>
+        <v>126417452</v>
       </c>
       <c r="B26" t="n">
-        <v>98265</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587398</v>
+        <v>587363</v>
       </c>
       <c r="R26" t="n">
-        <v>6986011</v>
+        <v>6985986</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,6 +3196,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Upprepande inom området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3421,10 +3421,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126419617</v>
+        <v>126418994</v>
       </c>
       <c r="B29" t="n">
-        <v>91541</v>
+        <v>57817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,34 +3432,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587192</v>
+        <v>587241</v>
       </c>
       <c r="R29" t="n">
-        <v>6986314</v>
+        <v>6986122</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,6 +3501,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>3 rör sig mellan träden pratar med varandra</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3518,10 +3532,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126416847</v>
+        <v>126419617</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>91541</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3543,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3567,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587406</v>
+        <v>587192</v>
       </c>
       <c r="R30" t="n">
-        <v>6985908</v>
+        <v>6986314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,10 +3629,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126421256</v>
+        <v>126416847</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,39 +3640,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587185</v>
+        <v>587406</v>
       </c>
       <c r="R31" t="n">
-        <v>6986510</v>
+        <v>6985908</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3691,11 +3700,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3722,7 +3726,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126419964</v>
+        <v>126421256</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3762,10 +3766,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586981</v>
+        <v>587185</v>
       </c>
       <c r="R32" t="n">
-        <v>6986245</v>
+        <v>6986510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3802,7 +3806,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3829,7 +3833,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126417368</v>
+        <v>126419964</v>
       </c>
       <c r="B33" t="n">
         <v>57657</v>
@@ -3869,10 +3873,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587328</v>
+        <v>586981</v>
       </c>
       <c r="R33" t="n">
-        <v>6985952</v>
+        <v>6986245</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126418994</v>
+        <v>126417368</v>
       </c>
       <c r="B34" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,31 +3951,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587241</v>
+        <v>587328</v>
       </c>
       <c r="R34" t="n">
-        <v>6986122</v>
+        <v>6985952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 rör sig mellan träden pratar med varandra</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4348,32 +4348,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126416472</v>
+        <v>126418669</v>
       </c>
       <c r="B38" t="n">
-        <v>80111</v>
+        <v>91245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587331</v>
+        <v>587315</v>
       </c>
       <c r="R38" t="n">
-        <v>6986098</v>
+        <v>6986068</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4445,32 +4445,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126418669</v>
+        <v>126416472</v>
       </c>
       <c r="B39" t="n">
-        <v>91245</v>
+        <v>80111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587315</v>
+        <v>587331</v>
       </c>
       <c r="R39" t="n">
-        <v>6986068</v>
+        <v>6986098</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4542,49 +4542,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126417679</v>
+        <v>126418977</v>
       </c>
       <c r="B40" t="n">
-        <v>98278</v>
+        <v>91245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587381</v>
+        <v>587250</v>
       </c>
       <c r="R40" t="n">
-        <v>6986014</v>
+        <v>6986130</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4617,11 +4613,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4648,49 +4639,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126416029</v>
+        <v>126419681</v>
       </c>
       <c r="B41" t="n">
-        <v>98278</v>
+        <v>91699</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587398</v>
+        <v>587210</v>
       </c>
       <c r="R41" t="n">
-        <v>6986000</v>
+        <v>6986334</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4749,45 +4736,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126418977</v>
+        <v>126417679</v>
       </c>
       <c r="B42" t="n">
-        <v>91245</v>
+        <v>98278</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587250</v>
+        <v>587381</v>
       </c>
       <c r="R42" t="n">
-        <v>6986130</v>
+        <v>6986014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,6 +4811,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4846,45 +4842,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126419681</v>
+        <v>126416029</v>
       </c>
       <c r="B43" t="n">
-        <v>91699</v>
+        <v>98278</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587210</v>
+        <v>587398</v>
       </c>
       <c r="R43" t="n">
-        <v>6986334</v>
+        <v>6986000</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126421920</v>
+        <v>126421544</v>
       </c>
       <c r="B45" t="n">
-        <v>91263</v>
+        <v>56840</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,34 +5051,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587478</v>
+        <v>587257</v>
       </c>
       <c r="R45" t="n">
-        <v>6986044</v>
+        <v>6986219</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5111,6 +5119,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Järpeunge som sitter på trädgrenen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5137,10 +5150,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126421544</v>
+        <v>126421920</v>
       </c>
       <c r="B46" t="n">
-        <v>56840</v>
+        <v>91263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5148,42 +5161,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587257</v>
+        <v>587478</v>
       </c>
       <c r="R46" t="n">
-        <v>6986219</v>
+        <v>6986044</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5216,11 +5221,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Järpeunge som sitter på trädgrenen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126417472</v>
+        <v>126416938</v>
       </c>
       <c r="B50" t="n">
-        <v>56233</v>
+        <v>88654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5579,39 +5579,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206004</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587363</v>
+        <v>587361</v>
       </c>
       <c r="R50" t="n">
-        <v>6985986</v>
+        <v>6985937</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5670,10 +5665,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126416938</v>
+        <v>126419739</v>
       </c>
       <c r="B51" t="n">
-        <v>88654</v>
+        <v>57657</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,34 +5676,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587361</v>
+        <v>587036</v>
       </c>
       <c r="R51" t="n">
-        <v>6985937</v>
+        <v>6986280</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5741,6 +5741,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5767,10 +5772,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126418565</v>
+        <v>126420043</v>
       </c>
       <c r="B52" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5778,37 +5783,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587314</v>
+        <v>587176</v>
       </c>
       <c r="R52" t="n">
-        <v>6986126</v>
+        <v>6986320</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5838,6 +5848,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall många</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5864,10 +5879,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126419122</v>
+        <v>126417472</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>56233</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5875,34 +5890,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587216</v>
+        <v>587363</v>
       </c>
       <c r="R53" t="n">
-        <v>6986114</v>
+        <v>6985986</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5961,10 +5981,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126419739</v>
+        <v>126418565</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>80083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5972,39 +5992,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>587036</v>
+        <v>587314</v>
       </c>
       <c r="R54" t="n">
-        <v>6986280</v>
+        <v>6986126</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6037,11 +6052,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6068,10 +6078,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126420043</v>
+        <v>126419122</v>
       </c>
       <c r="B55" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6079,42 +6089,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>587176</v>
+        <v>587216</v>
       </c>
       <c r="R55" t="n">
-        <v>6986320</v>
+        <v>6986114</v>
       </c>
       <c r="S55" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6144,11 +6149,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall många</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6879,10 +6879,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126418597</v>
+        <v>126420605</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6890,34 +6890,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>587303</v>
+        <v>587012</v>
       </c>
       <c r="R63" t="n">
-        <v>6986119</v>
+        <v>6986341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6950,6 +6955,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6976,38 +6986,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126420605</v>
+        <v>126416113</v>
       </c>
       <c r="B64" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7016,10 +7025,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587012</v>
+        <v>587402</v>
       </c>
       <c r="R64" t="n">
-        <v>6986341</v>
+        <v>6985981</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7056,7 +7065,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Riklig förekomst inom området 10+</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7083,49 +7092,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126416113</v>
+        <v>126418597</v>
       </c>
       <c r="B65" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587402</v>
+        <v>587303</v>
       </c>
       <c r="R65" t="n">
-        <v>6985981</v>
+        <v>6986119</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7158,11 +7163,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området 10+</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7189,50 +7189,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126420995</v>
+        <v>126418130</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>587147</v>
+        <v>587352</v>
       </c>
       <c r="R66" t="n">
-        <v>6986409</v>
+        <v>6986053</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7269,7 +7264,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Riklig förekomst av dom inom området</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7296,45 +7291,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126418130</v>
+        <v>126420995</v>
       </c>
       <c r="B67" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>587352</v>
+        <v>587147</v>
       </c>
       <c r="R67" t="n">
-        <v>6986053</v>
+        <v>6986409</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Riklig förekomst av dom inom området</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126416142</v>
+        <v>126418710</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,39 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587352</v>
+        <v>587267</v>
       </c>
       <c r="R6" t="n">
-        <v>6986053</v>
+        <v>6986111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,11 +1158,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126418710</v>
+        <v>126416142</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,34 +1195,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587267</v>
+        <v>587352</v>
       </c>
       <c r="R7" t="n">
-        <v>6986111</v>
+        <v>6986053</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,6 +1260,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -4047,50 +4047,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126421388</v>
+        <v>126419468</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>98278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587216</v>
+        <v>587187</v>
       </c>
       <c r="R35" t="n">
-        <v>6986485</v>
+        <v>6986221</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,11 +4118,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4154,32 +4144,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126419468</v>
+        <v>126419223</v>
       </c>
       <c r="B36" t="n">
-        <v>98278</v>
+        <v>80083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4189,10 +4179,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587187</v>
+        <v>587226</v>
       </c>
       <c r="R36" t="n">
-        <v>6986221</v>
+        <v>6986030</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4251,10 +4241,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126419223</v>
+        <v>126421388</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,34 +4252,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587226</v>
+        <v>587216</v>
       </c>
       <c r="R37" t="n">
-        <v>6986030</v>
+        <v>6986485</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4322,6 +4317,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126417916</v>
+        <v>126421649</v>
       </c>
       <c r="B56" t="n">
-        <v>91263</v>
+        <v>80084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6186,21 +6186,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587395</v>
+        <v>587297</v>
       </c>
       <c r="R56" t="n">
-        <v>6986032</v>
+        <v>6986177</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6272,10 +6272,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126421649</v>
+        <v>126417916</v>
       </c>
       <c r="B57" t="n">
-        <v>80084</v>
+        <v>91263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6283,21 +6283,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587297</v>
+        <v>587395</v>
       </c>
       <c r="R57" t="n">
-        <v>6986177</v>
+        <v>6986032</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126418710</v>
+        <v>126416142</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1098,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587267</v>
+        <v>587352</v>
       </c>
       <c r="R6" t="n">
-        <v>6986111</v>
+        <v>6986053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,6 +1163,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126416142</v>
+        <v>126418710</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,39 +1205,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587352</v>
+        <v>587267</v>
       </c>
       <c r="R7" t="n">
-        <v>6986053</v>
+        <v>6986111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,11 +1265,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126419276</v>
+        <v>126419173</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,39 +1705,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587199</v>
+        <v>587228</v>
       </c>
       <c r="R12" t="n">
-        <v>6986088</v>
+        <v>6986166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,11 +1765,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1801,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126416247</v>
+        <v>126421307</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,39 +1802,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587340</v>
+        <v>587162</v>
       </c>
       <c r="R13" t="n">
-        <v>6986065</v>
+        <v>6986535</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1908,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126419173</v>
+        <v>126419158</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587228</v>
+        <v>587227</v>
       </c>
       <c r="R14" t="n">
-        <v>6986166</v>
+        <v>6986101</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126421307</v>
+        <v>126419276</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,34 +1996,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587162</v>
+        <v>587199</v>
       </c>
       <c r="R15" t="n">
-        <v>6986535</v>
+        <v>6986088</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,6 +2061,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,45 +2092,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126419158</v>
+        <v>126416247</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587227</v>
+        <v>587340</v>
       </c>
       <c r="R16" t="n">
-        <v>6986101</v>
+        <v>6986065</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,6 +2168,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4736,49 +4736,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126417679</v>
+        <v>126421008</v>
       </c>
       <c r="B42" t="n">
-        <v>98278</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587381</v>
+        <v>587170</v>
       </c>
       <c r="R42" t="n">
-        <v>6986014</v>
+        <v>6986399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4811,11 +4807,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4842,7 +4833,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126416029</v>
+        <v>126417679</v>
       </c>
       <c r="B43" t="n">
         <v>98278</v>
@@ -4872,7 +4863,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4881,10 +4872,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587398</v>
+        <v>587381</v>
       </c>
       <c r="R43" t="n">
-        <v>6986000</v>
+        <v>6986014</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,6 +4908,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4943,45 +4939,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126421008</v>
+        <v>126416029</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>98278</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587170</v>
+        <v>587398</v>
       </c>
       <c r="R44" t="n">
-        <v>6986399</v>
+        <v>6986000</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126419173</v>
+        <v>126419276</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,34 +1705,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587228</v>
+        <v>587199</v>
       </c>
       <c r="R12" t="n">
-        <v>6986166</v>
+        <v>6986088</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,6 +1770,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126421307</v>
+        <v>126416247</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,34 +1812,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587162</v>
+        <v>587340</v>
       </c>
       <c r="R13" t="n">
-        <v>6986535</v>
+        <v>6986065</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1877,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,32 +1908,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126419158</v>
+        <v>126419173</v>
       </c>
       <c r="B14" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587227</v>
+        <v>587228</v>
       </c>
       <c r="R14" t="n">
-        <v>6986101</v>
+        <v>6986166</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126419276</v>
+        <v>126421307</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,39 +2016,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587199</v>
+        <v>587162</v>
       </c>
       <c r="R15" t="n">
-        <v>6986088</v>
+        <v>6986535</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,11 +2076,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2092,50 +2102,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126416247</v>
+        <v>126419158</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587340</v>
+        <v>587227</v>
       </c>
       <c r="R16" t="n">
-        <v>6986065</v>
+        <v>6986101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,11 +2173,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2612,45 +2612,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126416041</v>
+        <v>126416898</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587357</v>
+        <v>587390</v>
       </c>
       <c r="R21" t="n">
-        <v>6986029</v>
+        <v>6985939</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,10 +2713,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126419908</v>
+        <v>126416041</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,39 +2724,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587178</v>
+        <v>587357</v>
       </c>
       <c r="R22" t="n">
-        <v>6986327</v>
+        <v>6986029</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,11 +2784,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Äldre hack som återanvänds där av färsk sav/kåda från hålen runnit ut.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,37 +2810,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126416898</v>
+        <v>126419908</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2855,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587390</v>
+        <v>587178</v>
       </c>
       <c r="R23" t="n">
-        <v>6985939</v>
+        <v>6986327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2891,6 +2886,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Äldre hack som återanvänds där av färsk sav/kåda från hålen runnit ut.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4736,45 +4736,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126421008</v>
+        <v>126417679</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>98278</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587170</v>
+        <v>587381</v>
       </c>
       <c r="R42" t="n">
-        <v>6986399</v>
+        <v>6986014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4807,6 +4811,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4833,7 +4842,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126417679</v>
+        <v>126416029</v>
       </c>
       <c r="B43" t="n">
         <v>98278</v>
@@ -4863,7 +4872,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4872,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587381</v>
+        <v>587398</v>
       </c>
       <c r="R43" t="n">
-        <v>6986014</v>
+        <v>6986000</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4908,11 +4917,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Återkommande inom området.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4939,49 +4943,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126416029</v>
+        <v>126421008</v>
       </c>
       <c r="B44" t="n">
-        <v>98278</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Utsikten, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587398</v>
+        <v>587170</v>
       </c>
       <c r="R44" t="n">
-        <v>6986000</v>
+        <v>6986399</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126421311</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126416142</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126419125</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>126419276</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126416247</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>126420358</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>126417127</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>126419908</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>126420423</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>126421256</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>126419964</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126417368</v>
       </c>
       <c r="B34" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>126421388</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126417263</v>
       </c>
       <c r="B47" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>126419436</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>126421034</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>126419739</v>
       </c>
       <c r="B51" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>126420043</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>126419079</v>
       </c>
       <c r="B58" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>126419561</v>
       </c>
       <c r="B59" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>126420605</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>126420995</v>
       </c>
       <c r="B67" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126421311</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126416142</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126419125</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>126419276</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126416247</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>126420358</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>126417127</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>126419908</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>126420423</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>126421256</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>126419964</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126417368</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>126421388</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126417263</v>
       </c>
       <c r="B47" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>126419436</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>126421034</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>126419739</v>
       </c>
       <c r="B51" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>126420043</v>
       </c>
       <c r="B52" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>126419079</v>
       </c>
       <c r="B58" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>126419561</v>
       </c>
       <c r="B59" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>126420605</v>
       </c>
       <c r="B63" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>126420995</v>
       </c>
       <c r="B67" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126421311</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126416142</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126419125</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>126419276</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126416247</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>126420358</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>126417127</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>126419908</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>126420423</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>126421256</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>126419964</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126417368</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>126421388</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126417263</v>
       </c>
       <c r="B47" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>126419436</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>126421034</v>
       </c>
       <c r="B49" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>126419739</v>
       </c>
       <c r="B51" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>126420043</v>
       </c>
       <c r="B52" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>126419079</v>
       </c>
       <c r="B58" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>126419561</v>
       </c>
       <c r="B59" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>126420605</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>126420995</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 26015-2025 artfynd.xlsx
+++ b/artfynd/A 26015-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126421311</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>126416142</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>126419125</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>126419276</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126416247</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>126420358</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>126417127</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>126419908</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>126420423</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>126421256</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>126419964</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126417368</v>
       </c>
       <c r="B34" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>126421388</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126417263</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>126419436</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>126421034</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>126419739</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>126420043</v>
       </c>
       <c r="B52" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>126419079</v>
       </c>
       <c r="B58" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>126419561</v>
       </c>
       <c r="B59" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>126420605</v>
       </c>
       <c r="B63" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>126420995</v>
       </c>
       <c r="B67" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
